--- a/artfynd/A 2270-2025 artfynd.xlsx
+++ b/artfynd/A 2270-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122314178</v>
+        <v>122314152</v>
       </c>
       <c r="B2" t="n">
-        <v>97129</v>
+        <v>57390</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,53 +687,49 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Jutakärr, Vg</t>
+          <t>Älvängen, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>329237</v>
+        <v>329204</v>
       </c>
       <c r="R2" t="n">
-        <v>6426099</v>
+        <v>6426086</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,7 +758,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +768,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Spår efter födosök i träd.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,7 +782,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122314152</v>
+        <v>122314178</v>
       </c>
       <c r="B3" t="n">
-        <v>57390</v>
+        <v>97129</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,49 +812,53 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Älvängen, Vg</t>
+          <t>Jutakärr, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>329204</v>
+        <v>329237</v>
       </c>
       <c r="R3" t="n">
-        <v>6426086</v>
+        <v>6426099</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -883,7 +887,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -893,12 +897,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Spår efter födosök i träd.</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,6 +906,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 2270-2025 artfynd.xlsx
+++ b/artfynd/A 2270-2025 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>122314178</v>
       </c>
       <c r="B3" t="n">
-        <v>97129</v>
+        <v>97139</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 2270-2025 artfynd.xlsx
+++ b/artfynd/A 2270-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122314152</v>
+        <v>122314178</v>
       </c>
       <c r="B2" t="n">
-        <v>57390</v>
+        <v>97139</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,49 +687,53 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Älvängen, Vg</t>
+          <t>Jutakärr, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>329204</v>
+        <v>329237</v>
       </c>
       <c r="R2" t="n">
-        <v>6426086</v>
+        <v>6426099</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -758,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -768,12 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Spår efter födosök i träd.</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,6 +781,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122314178</v>
+        <v>122314152</v>
       </c>
       <c r="B3" t="n">
-        <v>97139</v>
+        <v>57390</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,53 +812,49 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Jutakärr, Vg</t>
+          <t>Älvängen, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>329237</v>
+        <v>329204</v>
       </c>
       <c r="R3" t="n">
-        <v>6426099</v>
+        <v>6426086</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -887,7 +883,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -897,7 +893,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Spår efter födosök i träd.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,7 +907,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 2270-2025 artfynd.xlsx
+++ b/artfynd/A 2270-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122314178</v>
       </c>
       <c r="B2" t="n">
-        <v>97139</v>
+        <v>97151</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>122314152</v>
       </c>
       <c r="B3" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 2270-2025 artfynd.xlsx
+++ b/artfynd/A 2270-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122314178</v>
       </c>
       <c r="B2" t="n">
-        <v>97151</v>
+        <v>97156</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 2270-2025 artfynd.xlsx
+++ b/artfynd/A 2270-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122314178</v>
+        <v>122314152</v>
       </c>
       <c r="B2" t="n">
-        <v>97156</v>
+        <v>57395</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,53 +687,44 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Jutakärr, Vg</t>
+          <t>Älvängen, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>329237</v>
+        <v>329204</v>
       </c>
       <c r="R2" t="n">
-        <v>6426099</v>
+        <v>6426086</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +763,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Spår efter födosök i träd.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,7 +777,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -800,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122314152</v>
+        <v>122314178</v>
       </c>
       <c r="B3" t="n">
-        <v>57395</v>
+        <v>97165</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,49 +807,48 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>221945</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Älvängen, Vg</t>
+          <t>Jutakärr, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>329204</v>
+        <v>329237</v>
       </c>
       <c r="R3" t="n">
-        <v>6426086</v>
+        <v>6426099</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -883,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -893,12 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Spår efter födosök i träd.</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,6 +896,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 2270-2025 artfynd.xlsx
+++ b/artfynd/A 2270-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122314152</v>
+        <v>122314178</v>
       </c>
       <c r="B2" t="n">
-        <v>57395</v>
+        <v>97178</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,44 +687,53 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>221945</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Älvängen, Vg</t>
+          <t>Jutakärr, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>329204</v>
+        <v>329237</v>
       </c>
       <c r="R2" t="n">
-        <v>6426086</v>
+        <v>6426099</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,12 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Spår efter födosök i träd.</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,6 +781,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -795,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122314178</v>
+        <v>122314152</v>
       </c>
       <c r="B3" t="n">
-        <v>97165</v>
+        <v>57399</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,48 +812,49 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Jutakärr, Vg</t>
+          <t>Älvängen, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>329237</v>
+        <v>329204</v>
       </c>
       <c r="R3" t="n">
-        <v>6426099</v>
+        <v>6426086</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,7 +883,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +893,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Spår efter födosök i träd.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,7 +907,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 2270-2025 artfynd.xlsx
+++ b/artfynd/A 2270-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122314178</v>
+        <v>122314152</v>
       </c>
       <c r="B2" t="n">
-        <v>97178</v>
+        <v>57399</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,53 +687,49 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Jutakärr, Vg</t>
+          <t>Älvängen, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>329237</v>
+        <v>329204</v>
       </c>
       <c r="R2" t="n">
-        <v>6426099</v>
+        <v>6426086</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,7 +758,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +768,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Spår efter födosök i träd.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,7 +782,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122314152</v>
+        <v>122314178</v>
       </c>
       <c r="B3" t="n">
-        <v>57399</v>
+        <v>97191</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,49 +812,53 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Älvängen, Vg</t>
+          <t>Jutakärr, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>329204</v>
+        <v>329237</v>
       </c>
       <c r="R3" t="n">
-        <v>6426086</v>
+        <v>6426099</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -883,7 +887,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -893,12 +897,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Spår efter födosök i träd.</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,6 +906,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 2270-2025 artfynd.xlsx
+++ b/artfynd/A 2270-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122314152</v>
+        <v>122314178</v>
       </c>
       <c r="B2" t="n">
-        <v>57399</v>
+        <v>97194</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,49 +687,53 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Älvängen, Vg</t>
+          <t>Jutakärr, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>329204</v>
+        <v>329237</v>
       </c>
       <c r="R2" t="n">
-        <v>6426086</v>
+        <v>6426099</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -758,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -768,12 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Spår efter födosök i träd.</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,6 +781,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122314178</v>
+        <v>122314152</v>
       </c>
       <c r="B3" t="n">
-        <v>97191</v>
+        <v>57399</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,53 +812,49 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Jutakärr, Vg</t>
+          <t>Älvängen, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>329237</v>
+        <v>329204</v>
       </c>
       <c r="R3" t="n">
-        <v>6426099</v>
+        <v>6426086</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -887,7 +883,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -897,7 +893,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Spår efter födosök i träd.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,7 +907,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 2270-2025 artfynd.xlsx
+++ b/artfynd/A 2270-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122314178</v>
+        <v>122314152</v>
       </c>
       <c r="B2" t="n">
-        <v>97198</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,49 +686,45 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Jutakärr, Vg</t>
+          <t>Älvängen, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>329237</v>
+        <v>329204</v>
       </c>
       <c r="R2" t="n">
-        <v>6426099</v>
+        <v>6426086</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +763,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Spår efter födosök i träd.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,7 +777,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -800,61 +795,60 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122314152</v>
+        <v>122314178</v>
       </c>
       <c r="B3" t="n">
-        <v>57400</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Älvängen, Vg</t>
+          <t>Jutakärr, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>329204</v>
+        <v>329237</v>
       </c>
       <c r="R3" t="n">
-        <v>6426086</v>
+        <v>6426099</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -883,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -893,12 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Spår efter födosök i träd.</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,6 +896,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 2270-2025 artfynd.xlsx
+++ b/artfynd/A 2270-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -792,6 +797,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122314152</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -912,8 +922,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122314178</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>